--- a/doc/Gantt_Sprint_Rivano.xlsx
+++ b/doc/Gantt_Sprint_Rivano.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cp-24tom\3eme_Annee\Codage\Car_Rental\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8665E570-6B8E-4C5D-AB9D-1D1500B79C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A28614-98FF-4081-9DCC-C71E1968FE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
   <si>
     <t>RIVANO - Avancement du sprint</t>
   </si>
@@ -85,24 +85,12 @@
     <t>A venir</t>
   </si>
   <si>
-    <t>7h25</t>
-  </si>
-  <si>
     <t>4h25</t>
   </si>
   <si>
-    <t>2h40</t>
-  </si>
-  <si>
     <t>7h30</t>
   </si>
   <si>
-    <t>2h55</t>
-  </si>
-  <si>
-    <t>en cours</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -200,6 +188,15 @@
   </si>
   <si>
     <t>Planification Trello (9 recits 0 a 8)</t>
+  </si>
+  <si>
+    <t>ve 04/09</t>
+  </si>
+  <si>
+    <t>5h25</t>
+  </si>
+  <si>
+    <t>3h55</t>
   </si>
 </sst>
 </file>
@@ -366,15 +363,15 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -808,15 +805,15 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="19"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
     <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B2" s="2"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
@@ -825,10 +822,10 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -856,46 +853,52 @@
         <v>10</v>
       </c>
       <c r="L4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="L5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8"/>
@@ -906,13 +909,14 @@
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
     </row>
     <row r="7" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
-        <v>50</v>
+      <c r="B7" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="8"/>
@@ -923,22 +927,22 @@
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
     </row>
     <row r="8" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="8"/>
@@ -949,22 +953,22 @@
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
     </row>
     <row r="9" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="8"/>
@@ -975,24 +979,24 @@
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23" t="e" vm="1">
+      <c r="M9" s="8"/>
+      <c r="N9" s="21" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
     </row>
     <row r="10" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -1003,22 +1007,22 @@
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
     </row>
     <row r="11" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="7"/>
@@ -1029,22 +1033,22 @@
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
     </row>
     <row r="12" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="9"/>
@@ -1055,22 +1059,22 @@
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
     </row>
     <row r="13" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="7"/>
@@ -1081,22 +1085,22 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
     </row>
     <row r="14" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -1107,22 +1111,22 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
     </row>
     <row r="15" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -1133,22 +1137,22 @@
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
     </row>
     <row r="16" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -1159,22 +1163,22 @@
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
     </row>
     <row r="17" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -1185,22 +1189,22 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
     </row>
     <row r="18" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -1211,22 +1215,22 @@
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
     </row>
     <row r="19" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -1237,22 +1241,22 @@
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
     </row>
     <row r="20" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -1263,22 +1267,22 @@
       <c r="J20" s="7"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
     </row>
     <row r="21" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -1289,22 +1293,22 @@
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
     </row>
     <row r="22" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -1314,23 +1318,23 @@
       <c r="I22" s="8"/>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
     </row>
     <row r="23" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -1340,23 +1344,23 @@
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="10"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
     </row>
     <row r="24" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -1366,23 +1370,23 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
     </row>
     <row r="25" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -1392,23 +1396,23 @@
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
     </row>
     <row r="26" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -1418,23 +1422,23 @@
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
     </row>
     <row r="27" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -1444,14 +1448,15 @@
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
-      <c r="L27" s="11"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
     </row>
     <row r="28" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -1461,44 +1466,45 @@
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
-      <c r="L28" s="11"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
+        <v>41</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
+        <v>42</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
+        <v>43</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="21"/>
+        <v>44</v>
+      </c>
+      <c r="C33" s="19"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="21"/>
+        <v>45</v>
+      </c>
+      <c r="C34" s="19"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="17"/>
